--- a/lakehouse/src/test/resources/ct/dna/lakehouse/dm_md/fin_hawk/MaktTest.xlsx
+++ b/lakehouse/src/test/resources/ct/dna/lakehouse/dm_md/fin_hawk/MaktTest.xlsx
@@ -55,13 +55,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFFACD"/>
+          <bgColor rgb="00FFFACD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -16887,6 +16898,11 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:R217">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(NOT(ISBLANK(A2)), LEN(A2)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33361,6 +33377,11 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:R217">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(NOT(ISBLANK(A2)), LEN(A2)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49835,6 +49856,11 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:R217">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(NOT(ISBLANK(A2)), LEN(A2)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -66309,6 +66335,11 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:R217">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(NOT(ISBLANK(A2)), LEN(A2)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -66626,7 +66657,11 @@
           <t>D_D01E06_pre</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -66659,7 +66694,11 @@
           <t>D_D01E07_pre</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -66692,7 +66731,11 @@
           <t>D_D01E08_pre</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -66725,7 +66768,11 @@
           <t>D_D01E09_pre</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -67039,7 +67086,11 @@
           <t>D_D02E06_pre</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -67072,7 +67123,11 @@
           <t>D_D02E07_pre</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -67105,7 +67160,11 @@
           <t>D_D02E08_pre</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -67138,7 +67197,11 @@
           <t>D_D02E09_pre</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -67452,7 +67515,11 @@
           <t>D_D03E06_same</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -67485,7 +67552,11 @@
           <t>D_D03E07_same</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -67518,7 +67589,11 @@
           <t>D_D03E08_same</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -67551,7 +67626,11 @@
           <t>D_D03E09_same</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -67865,7 +67944,11 @@
           <t>D_D04E06_same</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -67898,7 +67981,11 @@
           <t>D_D04E07_same</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -67931,7 +68018,11 @@
           <t>D_D04E08_same</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -67964,7 +68055,11 @@
           <t>D_D04E09_same</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -68278,7 +68373,11 @@
           <t>D_D05E06_pre</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -68311,7 +68410,11 @@
           <t>D_D05E07_pre</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -68344,7 +68447,11 @@
           <t>D_D05E08_pre</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -68377,7 +68484,11 @@
           <t>D_D05E09_pre</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -68501,7 +68612,11 @@
           <t>~~E_D06E01_pre</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>E_D06E01_pre</t>
@@ -68534,7 +68649,11 @@
           <t>~~E_D06E02_pre</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>E_D06E02_pre</t>
@@ -68567,7 +68686,11 @@
           <t>~~E_D06E03_same</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>E_D06E03_same</t>
@@ -68600,7 +68723,11 @@
           <t>~~E_D06E04_same</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>E_D06E04_same</t>
@@ -68633,7 +68760,11 @@
           <t>~~E_D06E05_pre</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>E_D06E05_pre</t>
@@ -68666,8 +68797,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -68695,8 +68834,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -68724,8 +68871,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -68753,8 +68908,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -68777,8 +68940,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -68801,8 +68972,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -68825,8 +69004,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -68854,7 +69041,11 @@
           <t>~~E_D07E01_pre</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
           <t>E_D07E01_pre</t>
@@ -68887,7 +69078,11 @@
           <t>~~E_D07E02_pre</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>E_D07E02_pre</t>
@@ -68920,7 +69115,11 @@
           <t>~~E_D07E03_same</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>E_D07E03_same</t>
@@ -68953,7 +69152,11 @@
           <t>~~E_D07E04_same</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>E_D07E04_same</t>
@@ -68986,7 +69189,11 @@
           <t>~~E_D07E05_pre</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
           <t>E_D07E05_pre</t>
@@ -69019,8 +69226,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -69048,8 +69263,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -69077,8 +69300,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -69106,8 +69337,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -69130,8 +69369,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -69154,8 +69401,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -69178,8 +69433,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -69207,7 +69470,11 @@
           <t>~~E_D08E01_pre</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
           <t>E_D08E01_pre</t>
@@ -69240,7 +69507,11 @@
           <t>~~E_D08E02_pre</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
           <t>E_D08E02_pre</t>
@@ -69273,7 +69544,11 @@
           <t>~~E_D08E03_same</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
           <t>E_D08E03_same</t>
@@ -69306,7 +69581,11 @@
           <t>~~E_D08E04_same</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
           <t>E_D08E04_same</t>
@@ -69339,7 +69618,11 @@
           <t>~~E_D08E05_pre</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
           <t>E_D08E05_pre</t>
@@ -69372,8 +69655,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -69401,8 +69692,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -69430,8 +69729,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -69459,8 +69766,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -69483,8 +69798,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -69507,8 +69830,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -69531,8 +69862,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -69560,7 +69899,11 @@
           <t>~~E_D09E01_pre</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>E_D09E01_pre</t>
@@ -69593,7 +69936,11 @@
           <t>~~E_D09E02_pre</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G99" t="inlineStr">
         <is>
           <t>E_D09E02_pre</t>
@@ -69626,7 +69973,11 @@
           <t>~~E_D09E03_same</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G100" t="inlineStr">
         <is>
           <t>E_D09E03_same</t>
@@ -69659,7 +70010,11 @@
           <t>~~E_D09E04_same</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
           <t>E_D09E04_same</t>
@@ -69692,7 +70047,11 @@
           <t>~~E_D09E05_pre</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
           <t>E_D09E05_pre</t>
@@ -69725,8 +70084,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -69754,8 +70121,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -69783,8 +70158,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -69812,8 +70195,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -69836,8 +70227,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -69860,8 +70259,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -69884,8 +70291,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -70068,8 +70483,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -70092,8 +70515,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -70116,8 +70547,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -70140,8 +70579,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -70324,8 +70771,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -70348,8 +70803,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -70372,8 +70835,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -70396,8 +70867,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -70580,8 +71059,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -70604,8 +71091,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -70628,8 +71123,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -70652,8 +71155,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -70871,7 +71382,11 @@
           <t>D_D01E06_pre</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -70904,7 +71419,11 @@
           <t>D_D01E07_pre</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -70937,7 +71456,11 @@
           <t>D_D01E08_pre</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -70970,7 +71493,11 @@
           <t>D_D01E09_pre</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -71284,7 +71811,11 @@
           <t>D_D02E06_pre</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -71317,7 +71848,11 @@
           <t>D_D02E07_pre</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -71350,7 +71885,11 @@
           <t>D_D02E08_pre</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -71383,7 +71922,11 @@
           <t>D_D02E09_pre</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -71697,7 +72240,11 @@
           <t>D_D03E06_same</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -71730,7 +72277,11 @@
           <t>D_D03E07_same</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr"/>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -71763,7 +72314,11 @@
           <t>D_D03E08_same</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -71796,7 +72351,11 @@
           <t>D_D03E09_same</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -72110,7 +72669,11 @@
           <t>D_D04E06_same</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -72143,7 +72706,11 @@
           <t>D_D04E07_same</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -72176,7 +72743,11 @@
           <t>D_D04E08_same</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -72209,7 +72780,11 @@
           <t>D_D04E09_same</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr"/>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -72523,7 +73098,11 @@
           <t>D_D05E06_pre</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr"/>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -72556,7 +73135,11 @@
           <t>D_D05E07_pre</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr"/>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -72589,7 +73172,11 @@
           <t>D_D05E08_pre</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -72622,7 +73209,11 @@
           <t>D_D05E09_pre</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr"/>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -72746,7 +73337,11 @@
           <t>~~E_D06E01_pre</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr"/>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G197" t="inlineStr">
         <is>
           <t>E_D06E01_pre</t>
@@ -72779,7 +73374,11 @@
           <t>~~E_D06E02_pre</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr"/>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G198" t="inlineStr">
         <is>
           <t>E_D06E02_pre</t>
@@ -72812,7 +73411,11 @@
           <t>~~E_D06E03_same</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr"/>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G199" t="inlineStr">
         <is>
           <t>E_D06E03_same</t>
@@ -72845,7 +73448,11 @@
           <t>~~E_D06E04_same</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr"/>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G200" t="inlineStr">
         <is>
           <t>E_D06E04_same</t>
@@ -72878,7 +73485,11 @@
           <t>~~E_D06E05_pre</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr"/>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G201" t="inlineStr">
         <is>
           <t>E_D06E05_pre</t>
@@ -72911,8 +73522,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -72940,8 +73559,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -72969,8 +73596,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -72998,8 +73633,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr"/>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -73022,8 +73665,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -73046,8 +73697,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -73070,8 +73729,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -73099,7 +73766,11 @@
           <t>~~E_D07E01_pre</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr"/>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G209" t="inlineStr">
         <is>
           <t>E_D07E01_pre</t>
@@ -73132,7 +73803,11 @@
           <t>~~E_D07E02_pre</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr"/>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G210" t="inlineStr">
         <is>
           <t>E_D07E02_pre</t>
@@ -73165,7 +73840,11 @@
           <t>~~E_D07E03_same</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr"/>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G211" t="inlineStr">
         <is>
           <t>E_D07E03_same</t>
@@ -73198,7 +73877,11 @@
           <t>~~E_D07E04_same</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr"/>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G212" t="inlineStr">
         <is>
           <t>E_D07E04_same</t>
@@ -73231,7 +73914,11 @@
           <t>~~E_D07E05_pre</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr"/>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G213" t="inlineStr">
         <is>
           <t>E_D07E05_pre</t>
@@ -73264,8 +73951,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr"/>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -73293,8 +73988,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr"/>
-      <c r="G215" t="inlineStr"/>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -73322,8 +74025,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr"/>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -73351,8 +74062,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr"/>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -73375,8 +74094,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -73399,8 +74126,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -73423,8 +74158,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -73452,7 +74195,11 @@
           <t>~~E_D08E01_pre</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr"/>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G221" t="inlineStr">
         <is>
           <t>E_D08E01_pre</t>
@@ -73485,7 +74232,11 @@
           <t>~~E_D08E02_pre</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr"/>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G222" t="inlineStr">
         <is>
           <t>E_D08E02_pre</t>
@@ -73518,7 +74269,11 @@
           <t>~~E_D08E03_same</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr"/>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G223" t="inlineStr">
         <is>
           <t>E_D08E03_same</t>
@@ -73551,7 +74306,11 @@
           <t>~~E_D08E04_same</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr"/>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G224" t="inlineStr">
         <is>
           <t>E_D08E04_same</t>
@@ -73584,7 +74343,11 @@
           <t>~~E_D08E05_pre</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr"/>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G225" t="inlineStr">
         <is>
           <t>E_D08E05_pre</t>
@@ -73617,8 +74380,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -73646,8 +74417,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -73675,8 +74454,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr"/>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -73704,8 +74491,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr"/>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -73728,8 +74523,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -73752,8 +74555,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -73776,8 +74587,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr"/>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -73805,7 +74624,11 @@
           <t>~~E_D09E01_pre</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr"/>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G233" t="inlineStr">
         <is>
           <t>E_D09E01_pre</t>
@@ -73838,7 +74661,11 @@
           <t>~~E_D09E02_pre</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr"/>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G234" t="inlineStr">
         <is>
           <t>E_D09E02_pre</t>
@@ -73871,7 +74698,11 @@
           <t>~~E_D09E03_same</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr"/>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G235" t="inlineStr">
         <is>
           <t>E_D09E03_same</t>
@@ -73904,7 +74735,11 @@
           <t>~~E_D09E04_same</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr"/>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G236" t="inlineStr">
         <is>
           <t>E_D09E04_same</t>
@@ -73937,7 +74772,11 @@
           <t>~~E_D09E05_pre</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr"/>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G237" t="inlineStr">
         <is>
           <t>E_D09E05_pre</t>
@@ -73970,8 +74809,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -73999,8 +74846,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr"/>
-      <c r="G239" t="inlineStr"/>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -74028,8 +74883,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr"/>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -74057,8 +74920,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr"/>
-      <c r="G241" t="inlineStr"/>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -74081,8 +74952,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -74105,8 +74984,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -74129,8 +75016,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -74313,8 +75208,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr"/>
-      <c r="G250" t="inlineStr"/>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -74337,8 +75240,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr"/>
-      <c r="G251" t="inlineStr"/>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -74361,8 +75272,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -74385,8 +75304,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr"/>
-      <c r="G253" t="inlineStr"/>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -74569,8 +75496,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -74593,8 +75528,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -74617,8 +75560,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -74641,8 +75592,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr"/>
-      <c r="G262" t="inlineStr"/>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -74825,8 +75784,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr"/>
-      <c r="G268" t="inlineStr"/>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -74849,8 +75816,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr"/>
-      <c r="G269" t="inlineStr"/>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -74873,8 +75848,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr"/>
-      <c r="G270" t="inlineStr"/>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -74897,10 +75880,23 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:G271">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(NOT(ISBLANK(A2)), LEN(A2)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -75019,7 +76015,11 @@
           <t>D_D01E02_post</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -75195,7 +76195,11 @@
           <t>D_D01E07_post</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -75228,7 +76232,11 @@
           <t>D_D01E08_post</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -75362,7 +76370,11 @@
           <t>D_D01E12_post</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -75390,7 +76402,11 @@
           <t>~~E_D02E01_post</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>E_D02E01_post</t>
@@ -75423,8 +76439,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -75452,7 +76476,11 @@
           <t>~~E_D02E03_same</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>E_D02E03_same</t>
@@ -75485,7 +76513,11 @@
           <t>~~E_D02E04_same</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>E_D02E04_same</t>
@@ -75513,8 +76545,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -75542,7 +76582,11 @@
           <t>~~E_D02E06_post</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>E_D02E06_post</t>
@@ -75575,8 +76619,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -75604,8 +76656,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -75628,8 +76688,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -75657,7 +76725,11 @@
           <t>~~E_D02E10_post</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>E_D02E10_post</t>
@@ -75685,8 +76757,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -75714,8 +76794,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -75785,7 +76873,11 @@
           <t>D_D03E02_same</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -75961,7 +77053,11 @@
           <t>D_D03E07_same</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -75994,7 +77090,11 @@
           <t>D_D03E08_same</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -76128,7 +77228,11 @@
           <t>D_D03E12_same</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -76198,7 +77302,11 @@
           <t>D_D04E02_same</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -76374,7 +77482,11 @@
           <t>D_D04E07_same</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -76407,7 +77519,11 @@
           <t>D_D04E08_same</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -76541,7 +77657,11 @@
           <t>D_D04E12_same</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -76596,8 +77716,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -76716,8 +77844,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -76740,8 +77876,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -76796,8 +77940,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -76867,7 +78019,11 @@
           <t>D_D06E02_post</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -77043,7 +78199,11 @@
           <t>D_D06E07_post</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -77076,7 +78236,11 @@
           <t>D_D06E08_post</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -77210,7 +78374,11 @@
           <t>D_D06E12_post</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -77238,7 +78406,11 @@
           <t>~~E_D07E01_post</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>E_D07E01_post</t>
@@ -77271,8 +78443,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -77300,7 +78480,11 @@
           <t>~~E_D07E03_same</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
           <t>E_D07E03_same</t>
@@ -77333,7 +78517,11 @@
           <t>~~E_D07E04_same</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
           <t>E_D07E04_same</t>
@@ -77361,8 +78549,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -77390,7 +78586,11 @@
           <t>~~E_D07E06_post</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>E_D07E06_post</t>
@@ -77423,8 +78623,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -77452,8 +78660,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -77476,8 +78692,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -77505,7 +78729,11 @@
           <t>~~E_D07E10_post</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
           <t>E_D07E10_post</t>
@@ -77533,8 +78761,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -77562,8 +78798,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -77591,7 +78835,11 @@
           <t>~~E_D08E01_post</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>E_D08E01_post</t>
@@ -77624,8 +78872,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -77653,7 +78909,11 @@
           <t>~~E_D08E03_same</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
           <t>E_D08E03_same</t>
@@ -77686,7 +78946,11 @@
           <t>~~E_D08E04_same</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
           <t>E_D08E04_same</t>
@@ -77714,8 +78978,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -77743,7 +79015,11 @@
           <t>~~E_D08E06_post</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
           <t>E_D08E06_post</t>
@@ -77776,8 +79052,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -77805,8 +79089,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -77829,8 +79121,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -77858,7 +79158,11 @@
           <t>~~E_D08E10_post</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
           <t>E_D08E10_post</t>
@@ -77886,8 +79190,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -77915,8 +79227,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -77971,8 +79291,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -78091,8 +79419,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -78115,8 +79451,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -78171,8 +79515,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -78242,7 +79594,11 @@
           <t>D_D10E02_post</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -78418,7 +79774,11 @@
           <t>D_D10E07_post</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -78451,7 +79811,11 @@
           <t>D_D10E08_post</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -78585,7 +79949,11 @@
           <t>D_D10E12_post</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -78640,8 +80008,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -78760,8 +80136,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -78784,8 +80168,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -78840,8 +80232,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -78869,7 +80269,11 @@
           <t>~~E_D12E01_post</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G125" t="inlineStr">
         <is>
           <t>E_D12E01_post</t>
@@ -78902,8 +80306,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -78931,7 +80343,11 @@
           <t>~~E_D12E03_same</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
           <t>E_D12E03_same</t>
@@ -78964,7 +80380,11 @@
           <t>~~E_D12E04_same</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
           <t>E_D12E04_same</t>
@@ -78992,8 +80412,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -79021,7 +80449,11 @@
           <t>~~E_D12E06_post</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G130" t="inlineStr">
         <is>
           <t>E_D12E06_post</t>
@@ -79054,8 +80486,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -79083,8 +80523,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -79107,8 +80555,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -79136,7 +80592,11 @@
           <t>~~E_D12E10_post</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G134" t="inlineStr">
         <is>
           <t>E_D12E10_post</t>
@@ -79164,8 +80624,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -79193,8 +80661,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -79412,7 +80888,11 @@
           <t>D_D01E06_pre</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -79445,7 +80925,11 @@
           <t>D_D01E07_pre</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -79478,7 +80962,11 @@
           <t>D_D01E08_pre</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -79511,7 +80999,11 @@
           <t>D_D01E09_pre</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -79825,7 +81317,11 @@
           <t>D_D02E06_pre</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -79858,7 +81354,11 @@
           <t>D_D02E07_pre</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -79891,7 +81391,11 @@
           <t>D_D02E08_pre</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -79924,7 +81428,11 @@
           <t>D_D02E09_pre</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -80238,7 +81746,11 @@
           <t>D_D03E06_same</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -80271,7 +81783,11 @@
           <t>D_D03E07_same</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr"/>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -80304,7 +81820,11 @@
           <t>D_D03E08_same</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -80337,7 +81857,11 @@
           <t>D_D03E09_same</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -80651,7 +82175,11 @@
           <t>D_D04E06_same</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -80684,7 +82212,11 @@
           <t>D_D04E07_same</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -80717,7 +82249,11 @@
           <t>D_D04E08_same</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -80750,7 +82286,11 @@
           <t>D_D04E09_same</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr"/>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -81064,7 +82604,11 @@
           <t>D_D05E06_pre</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr"/>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -81097,7 +82641,11 @@
           <t>D_D05E07_pre</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr"/>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -81130,7 +82678,11 @@
           <t>D_D05E08_pre</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -81163,7 +82715,11 @@
           <t>D_D05E09_pre</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr"/>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -81287,7 +82843,11 @@
           <t>~~E_D06E01_pre</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr"/>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G197" t="inlineStr">
         <is>
           <t>E_D06E01_pre</t>
@@ -81320,7 +82880,11 @@
           <t>~~E_D06E02_pre</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr"/>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G198" t="inlineStr">
         <is>
           <t>E_D06E02_pre</t>
@@ -81353,7 +82917,11 @@
           <t>~~E_D06E03_same</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr"/>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G199" t="inlineStr">
         <is>
           <t>E_D06E03_same</t>
@@ -81386,7 +82954,11 @@
           <t>~~E_D06E04_same</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr"/>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G200" t="inlineStr">
         <is>
           <t>E_D06E04_same</t>
@@ -81419,7 +82991,11 @@
           <t>~~E_D06E05_pre</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr"/>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G201" t="inlineStr">
         <is>
           <t>E_D06E05_pre</t>
@@ -81452,8 +83028,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -81481,8 +83065,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -81510,8 +83102,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -81539,8 +83139,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr"/>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -81563,8 +83171,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -81587,8 +83203,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -81611,8 +83235,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -81640,7 +83272,11 @@
           <t>~~E_D07E01_pre</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr"/>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G209" t="inlineStr">
         <is>
           <t>E_D07E01_pre</t>
@@ -81673,7 +83309,11 @@
           <t>~~E_D07E02_pre</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr"/>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G210" t="inlineStr">
         <is>
           <t>E_D07E02_pre</t>
@@ -81706,7 +83346,11 @@
           <t>~~E_D07E03_same</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr"/>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G211" t="inlineStr">
         <is>
           <t>E_D07E03_same</t>
@@ -81739,7 +83383,11 @@
           <t>~~E_D07E04_same</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr"/>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G212" t="inlineStr">
         <is>
           <t>E_D07E04_same</t>
@@ -81772,7 +83420,11 @@
           <t>~~E_D07E05_pre</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr"/>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G213" t="inlineStr">
         <is>
           <t>E_D07E05_pre</t>
@@ -81805,8 +83457,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr"/>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -81834,8 +83494,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr"/>
-      <c r="G215" t="inlineStr"/>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -81863,8 +83531,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr"/>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -81892,8 +83568,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr"/>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -81916,8 +83600,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -81940,8 +83632,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -81964,8 +83664,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -81993,7 +83701,11 @@
           <t>~~E_D08E01_pre</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr"/>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G221" t="inlineStr">
         <is>
           <t>E_D08E01_pre</t>
@@ -82026,7 +83738,11 @@
           <t>~~E_D08E02_pre</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr"/>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G222" t="inlineStr">
         <is>
           <t>E_D08E02_pre</t>
@@ -82059,7 +83775,11 @@
           <t>~~E_D08E03_same</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr"/>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G223" t="inlineStr">
         <is>
           <t>E_D08E03_same</t>
@@ -82092,7 +83812,11 @@
           <t>~~E_D08E04_same</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr"/>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G224" t="inlineStr">
         <is>
           <t>E_D08E04_same</t>
@@ -82125,7 +83849,11 @@
           <t>~~E_D08E05_pre</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr"/>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G225" t="inlineStr">
         <is>
           <t>E_D08E05_pre</t>
@@ -82158,8 +83886,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -82187,8 +83923,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -82216,8 +83960,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr"/>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -82245,8 +83997,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr"/>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -82269,8 +84029,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -82293,8 +84061,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -82317,8 +84093,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr"/>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -82346,7 +84130,11 @@
           <t>~~E_D09E01_pre</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr"/>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G233" t="inlineStr">
         <is>
           <t>E_D09E01_pre</t>
@@ -82379,7 +84167,11 @@
           <t>~~E_D09E02_pre</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr"/>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G234" t="inlineStr">
         <is>
           <t>E_D09E02_pre</t>
@@ -82412,7 +84204,11 @@
           <t>~~E_D09E03_same</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr"/>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G235" t="inlineStr">
         <is>
           <t>E_D09E03_same</t>
@@ -82445,7 +84241,11 @@
           <t>~~E_D09E04_same</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr"/>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G236" t="inlineStr">
         <is>
           <t>E_D09E04_same</t>
@@ -82478,7 +84278,11 @@
           <t>~~E_D09E05_pre</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr"/>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G237" t="inlineStr">
         <is>
           <t>E_D09E05_pre</t>
@@ -82511,8 +84315,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -82540,8 +84352,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr"/>
-      <c r="G239" t="inlineStr"/>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -82569,8 +84389,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr"/>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -82598,8 +84426,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr"/>
-      <c r="G241" t="inlineStr"/>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -82622,8 +84458,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -82646,8 +84490,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -82670,8 +84522,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -82854,8 +84714,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr"/>
-      <c r="G250" t="inlineStr"/>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -82878,8 +84746,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr"/>
-      <c r="G251" t="inlineStr"/>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -82902,8 +84778,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -82926,8 +84810,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr"/>
-      <c r="G253" t="inlineStr"/>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -83110,8 +85002,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -83134,8 +85034,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -83158,8 +85066,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -83182,8 +85098,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr"/>
-      <c r="G262" t="inlineStr"/>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -83366,8 +85290,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr"/>
-      <c r="G268" t="inlineStr"/>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -83390,8 +85322,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr"/>
-      <c r="G269" t="inlineStr"/>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -83414,8 +85354,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr"/>
-      <c r="G270" t="inlineStr"/>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -83438,10 +85386,23 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:G271">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(NOT(ISBLANK(A2)), LEN(A2)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -83560,7 +85521,11 @@
           <t>D_D01E02_post</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -83736,7 +85701,11 @@
           <t>D_D01E07_post</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -83769,7 +85738,11 @@
           <t>D_D01E08_post</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -83903,7 +85876,11 @@
           <t>D_D01E12_post</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -83931,7 +85908,11 @@
           <t>~~E_D02E01_post</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>E_D02E01_post</t>
@@ -83964,8 +85945,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -83993,7 +85982,11 @@
           <t>~~E_D02E03_same</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>E_D02E03_same</t>
@@ -84026,7 +86019,11 @@
           <t>~~E_D02E04_same</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>E_D02E04_same</t>
@@ -84054,8 +86051,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -84083,7 +86088,11 @@
           <t>~~E_D02E06_post</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>E_D02E06_post</t>
@@ -84116,8 +86125,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -84145,8 +86162,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -84169,8 +86194,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -84198,7 +86231,11 @@
           <t>~~E_D02E10_post</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>E_D02E10_post</t>
@@ -84226,8 +86263,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -84255,8 +86300,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -84326,7 +86379,11 @@
           <t>D_D03E02_same</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -84502,7 +86559,11 @@
           <t>D_D03E07_same</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -84535,7 +86596,11 @@
           <t>D_D03E08_same</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -84669,7 +86734,11 @@
           <t>D_D03E12_same</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -84739,7 +86808,11 @@
           <t>D_D04E02_same</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -84915,7 +86988,11 @@
           <t>D_D04E07_same</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -84948,7 +87025,11 @@
           <t>D_D04E08_same</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -85082,7 +87163,11 @@
           <t>D_D04E12_same</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -85137,8 +87222,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -85257,8 +87350,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -85281,8 +87382,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -85337,8 +87446,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -85408,7 +87525,11 @@
           <t>D_D06E02_post</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -85584,7 +87705,11 @@
           <t>D_D06E07_post</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -85617,7 +87742,11 @@
           <t>D_D06E08_post</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -85751,7 +87880,11 @@
           <t>D_D06E12_post</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -85779,7 +87912,11 @@
           <t>~~E_D07E01_post</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>E_D07E01_post</t>
@@ -85812,8 +87949,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -85841,7 +87986,11 @@
           <t>~~E_D07E03_same</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
           <t>E_D07E03_same</t>
@@ -85874,7 +88023,11 @@
           <t>~~E_D07E04_same</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
           <t>E_D07E04_same</t>
@@ -85902,8 +88055,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -85931,7 +88092,11 @@
           <t>~~E_D07E06_post</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>E_D07E06_post</t>
@@ -85964,8 +88129,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -85993,8 +88166,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -86017,8 +88198,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -86046,7 +88235,11 @@
           <t>~~E_D07E10_post</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
           <t>E_D07E10_post</t>
@@ -86074,8 +88267,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -86103,8 +88304,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -86132,7 +88341,11 @@
           <t>~~E_D08E01_post</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>E_D08E01_post</t>
@@ -86165,8 +88378,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -86194,7 +88415,11 @@
           <t>~~E_D08E03_same</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
           <t>E_D08E03_same</t>
@@ -86227,7 +88452,11 @@
           <t>~~E_D08E04_same</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
           <t>E_D08E04_same</t>
@@ -86255,8 +88484,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -86284,7 +88521,11 @@
           <t>~~E_D08E06_post</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
           <t>E_D08E06_post</t>
@@ -86317,8 +88558,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -86346,8 +88595,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -86370,8 +88627,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -86399,7 +88664,11 @@
           <t>~~E_D08E10_post</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
           <t>E_D08E10_post</t>
@@ -86427,8 +88696,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -86456,8 +88733,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -86512,8 +88797,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -86632,8 +88925,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -86656,8 +88957,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -86712,8 +89021,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -86783,7 +89100,11 @@
           <t>D_D10E02_post</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -86959,7 +89280,11 @@
           <t>D_D10E07_post</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -86992,7 +89317,11 @@
           <t>D_D10E08_post</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -87126,7 +89455,11 @@
           <t>D_D10E12_post</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -87181,8 +89514,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -87301,8 +89642,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -87325,8 +89674,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -87381,8 +89738,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -87410,7 +89775,11 @@
           <t>~~E_D12E01_post</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G125" t="inlineStr">
         <is>
           <t>E_D12E01_post</t>
@@ -87443,8 +89812,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -87472,7 +89849,11 @@
           <t>~~E_D12E03_same</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
           <t>E_D12E03_same</t>
@@ -87505,7 +89886,11 @@
           <t>~~E_D12E04_same</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
           <t>E_D12E04_same</t>
@@ -87533,8 +89918,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -87562,7 +89955,11 @@
           <t>~~E_D12E06_post</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G130" t="inlineStr">
         <is>
           <t>E_D12E06_post</t>
@@ -87595,8 +89992,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -87624,8 +90029,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -87648,8 +90061,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -87677,7 +90098,11 @@
           <t>~~E_D12E10_post</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G134" t="inlineStr">
         <is>
           <t>E_D12E10_post</t>
@@ -87705,8 +90130,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -87734,8 +90167,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -87805,7 +90246,11 @@
           <t>D_D01E02_post</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -87981,7 +90426,11 @@
           <t>D_D01E07_post</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -88014,7 +90463,11 @@
           <t>D_D01E08_post</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -88148,7 +90601,11 @@
           <t>D_D01E12_post</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -88176,7 +90633,11 @@
           <t>~~E_D02E01_post</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G149" t="inlineStr">
         <is>
           <t>E_D02E01_post</t>
@@ -88209,8 +90670,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -88238,7 +90707,11 @@
           <t>~~E_D02E03_same</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G151" t="inlineStr">
         <is>
           <t>E_D02E03_same</t>
@@ -88271,7 +90744,11 @@
           <t>~~E_D02E04_same</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G152" t="inlineStr">
         <is>
           <t>E_D02E04_same</t>
@@ -88299,8 +90776,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -88328,7 +90813,11 @@
           <t>~~E_D02E06_post</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr"/>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G154" t="inlineStr">
         <is>
           <t>E_D02E06_post</t>
@@ -88361,8 +90850,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -88390,8 +90887,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -88414,8 +90919,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -88443,7 +90956,11 @@
           <t>~~E_D02E10_post</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G158" t="inlineStr">
         <is>
           <t>E_D02E10_post</t>
@@ -88471,8 +90988,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -88500,8 +91025,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -88571,7 +91104,11 @@
           <t>D_D03E02_same</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr"/>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -88747,7 +91284,11 @@
           <t>D_D03E07_same</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr"/>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -88780,7 +91321,11 @@
           <t>D_D03E08_same</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -88914,7 +91459,11 @@
           <t>D_D03E12_same</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -88984,7 +91533,11 @@
           <t>D_D04E02_same</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr"/>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -89160,7 +91713,11 @@
           <t>D_D04E07_same</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -89193,7 +91750,11 @@
           <t>D_D04E08_same</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -89327,7 +91888,11 @@
           <t>D_D04E12_same</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -89382,8 +91947,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -89502,8 +92075,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -89526,8 +92107,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -89582,8 +92171,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -89653,7 +92250,11 @@
           <t>D_D06E02_post</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -89829,7 +92430,11 @@
           <t>D_D06E07_post</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr"/>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -89862,7 +92467,11 @@
           <t>D_D06E08_post</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr"/>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -89996,7 +92605,11 @@
           <t>D_D06E12_post</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr"/>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -90024,7 +92637,11 @@
           <t>~~E_D07E01_post</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr"/>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G206" t="inlineStr">
         <is>
           <t>E_D07E01_post</t>
@@ -90057,8 +92674,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr"/>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -90086,7 +92711,11 @@
           <t>~~E_D07E03_same</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr"/>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G208" t="inlineStr">
         <is>
           <t>E_D07E03_same</t>
@@ -90119,7 +92748,11 @@
           <t>~~E_D07E04_same</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr"/>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G209" t="inlineStr">
         <is>
           <t>E_D07E04_same</t>
@@ -90147,8 +92780,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr"/>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -90176,7 +92817,11 @@
           <t>~~E_D07E06_post</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr"/>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G211" t="inlineStr">
         <is>
           <t>E_D07E06_post</t>
@@ -90209,8 +92854,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr"/>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -90238,8 +92891,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr"/>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -90262,8 +92923,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr"/>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -90291,7 +92960,11 @@
           <t>~~E_D07E10_post</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr"/>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G215" t="inlineStr">
         <is>
           <t>E_D07E10_post</t>
@@ -90319,8 +92992,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr"/>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -90348,8 +93029,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr"/>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -90377,7 +93066,11 @@
           <t>~~E_D08E01_post</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr"/>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G218" t="inlineStr">
         <is>
           <t>E_D08E01_post</t>
@@ -90410,8 +93103,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -90439,7 +93140,11 @@
           <t>~~E_D08E03_same</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr"/>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G220" t="inlineStr">
         <is>
           <t>E_D08E03_same</t>
@@ -90472,7 +93177,11 @@
           <t>~~E_D08E04_same</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr"/>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G221" t="inlineStr">
         <is>
           <t>E_D08E04_same</t>
@@ -90500,8 +93209,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -90529,7 +93246,11 @@
           <t>~~E_D08E06_post</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr"/>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G223" t="inlineStr">
         <is>
           <t>E_D08E06_post</t>
@@ -90562,8 +93283,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -90591,8 +93320,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr"/>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -90615,8 +93352,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -90644,7 +93389,11 @@
           <t>~~E_D08E10_post</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr"/>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G227" t="inlineStr">
         <is>
           <t>E_D08E10_post</t>
@@ -90672,8 +93421,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr"/>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -90701,8 +93458,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr"/>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -90757,8 +93522,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -90877,8 +93650,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr"/>
-      <c r="G235" t="inlineStr"/>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -90901,8 +93682,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr"/>
-      <c r="G236" t="inlineStr"/>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -90957,8 +93746,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -91028,7 +93825,11 @@
           <t>D_D10E02_post</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr"/>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -91204,7 +94005,11 @@
           <t>D_D10E07_post</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr"/>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -91237,7 +94042,11 @@
           <t>D_D10E08_post</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr"/>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -91371,7 +94180,11 @@
           <t>D_D10E12_post</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr"/>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -91426,8 +94239,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -91546,8 +94367,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr"/>
-      <c r="G256" t="inlineStr"/>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -91570,8 +94399,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr"/>
-      <c r="G257" t="inlineStr"/>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -91626,8 +94463,16 @@
           <t>E</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -91655,7 +94500,11 @@
           <t>~~E_D12E01_post</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr"/>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G260" t="inlineStr">
         <is>
           <t>E_D12E01_post</t>
@@ -91688,8 +94537,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -91717,7 +94574,11 @@
           <t>~~E_D12E03_same</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr"/>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G262" t="inlineStr">
         <is>
           <t>E_D12E03_same</t>
@@ -91750,7 +94611,11 @@
           <t>~~E_D12E04_same</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr"/>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G263" t="inlineStr">
         <is>
           <t>E_D12E04_same</t>
@@ -91778,8 +94643,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -91807,7 +94680,11 @@
           <t>~~E_D12E06_post</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr"/>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G265" t="inlineStr">
         <is>
           <t>E_D12E06_post</t>
@@ -91840,8 +94717,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr"/>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -91869,8 +94754,16 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr"/>
-      <c r="G267" t="inlineStr"/>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -91893,8 +94786,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr"/>
-      <c r="F268" t="inlineStr"/>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -91922,7 +94823,11 @@
           <t>~~E_D12E10_post</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr"/>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="G269" t="inlineStr">
         <is>
           <t>E_D12E10_post</t>
@@ -91950,8 +94855,16 @@
           <t>D</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr"/>
-      <c r="F270" t="inlineStr"/>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -91979,10 +94892,23 @@
           <t>~~</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:G271">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(NOT(ISBLANK(A2)), LEN(A2)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>